--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,790 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127843073</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>445421</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7039444</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127843069</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>445397</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7039448</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127843068</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>445329</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7039252</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127843089</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>445297</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7039205</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127843097</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100638</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>445498</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7039495</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127843096</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100638</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445438</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039487</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127843065</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039366</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127843087</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91334</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445301</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039216</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -801,53 +801,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843073</v>
+        <v>127843069</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>92038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445421</v>
+        <v>445397</v>
       </c>
       <c r="R3" t="n">
-        <v>7039444</v>
+        <v>7039448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,45 +898,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843069</v>
+        <v>127843073</v>
       </c>
       <c r="B4" t="n">
-        <v>92035</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445397</v>
+        <v>445421</v>
       </c>
       <c r="R4" t="n">
-        <v>7039448</v>
+        <v>7039444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,32 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843068</v>
+        <v>127843089</v>
       </c>
       <c r="B5" t="n">
-        <v>92035</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445329</v>
+        <v>445297</v>
       </c>
       <c r="R5" t="n">
-        <v>7039252</v>
+        <v>7039205</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,32 +1100,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843089</v>
+        <v>127843068</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>92038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445297</v>
+        <v>445329</v>
       </c>
       <c r="R6" t="n">
-        <v>7039205</v>
+        <v>7039252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -801,45 +801,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843069</v>
+        <v>127843073</v>
       </c>
       <c r="B3" t="n">
-        <v>92038</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445397</v>
+        <v>445421</v>
       </c>
       <c r="R3" t="n">
-        <v>7039448</v>
+        <v>7039444</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,53 +906,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843073</v>
+        <v>127843069</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445421</v>
+        <v>445397</v>
       </c>
       <c r="R4" t="n">
-        <v>7039444</v>
+        <v>7039448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,32 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843089</v>
+        <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445297</v>
+        <v>445329</v>
       </c>
       <c r="R5" t="n">
-        <v>7039205</v>
+        <v>7039252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,32 +1100,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843068</v>
+        <v>127843089</v>
       </c>
       <c r="B6" t="n">
-        <v>92038</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445329</v>
+        <v>445297</v>
       </c>
       <c r="R6" t="n">
-        <v>7039252</v>
+        <v>7039205</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>127843069</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,32 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843068</v>
+        <v>127843089</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445329</v>
+        <v>445297</v>
       </c>
       <c r="R5" t="n">
-        <v>7039252</v>
+        <v>7039205</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,32 +1100,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843089</v>
+        <v>127843068</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>92047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445297</v>
+        <v>445329</v>
       </c>
       <c r="R6" t="n">
-        <v>7039205</v>
+        <v>7039252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1003,32 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843089</v>
+        <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>92047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445297</v>
+        <v>445329</v>
       </c>
       <c r="R5" t="n">
-        <v>7039205</v>
+        <v>7039252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,32 +1100,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843068</v>
+        <v>127843089</v>
       </c>
       <c r="B6" t="n">
-        <v>92047</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445329</v>
+        <v>445297</v>
       </c>
       <c r="R6" t="n">
-        <v>7039252</v>
+        <v>7039205</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>127843069</v>
       </c>
       <c r="B4" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>127843069</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -801,53 +801,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843073</v>
+        <v>127843069</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>92049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445421</v>
+        <v>445397</v>
       </c>
       <c r="R3" t="n">
-        <v>7039444</v>
+        <v>7039448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,45 +898,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843069</v>
+        <v>127843073</v>
       </c>
       <c r="B4" t="n">
-        <v>92049</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445397</v>
+        <v>445421</v>
       </c>
       <c r="R4" t="n">
-        <v>7039448</v>
+        <v>7039444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>127843069</v>
       </c>
       <c r="B3" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127843073</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127843089</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -801,45 +801,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843069</v>
+        <v>127843073</v>
       </c>
       <c r="B3" t="n">
-        <v>92057</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445397</v>
+        <v>445421</v>
       </c>
       <c r="R3" t="n">
-        <v>7039448</v>
+        <v>7039444</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,53 +906,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843073</v>
+        <v>127843069</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445421</v>
+        <v>445397</v>
       </c>
       <c r="R4" t="n">
-        <v>7039444</v>
+        <v>7039448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843068</v>
+        <v>127843097</v>
       </c>
       <c r="B5" t="n">
-        <v>92057</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445329</v>
+        <v>445498</v>
       </c>
       <c r="R5" t="n">
-        <v>7039252</v>
+        <v>7039495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
         <v>127843089</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843097</v>
+        <v>127843068</v>
       </c>
       <c r="B7" t="n">
-        <v>100660</v>
+        <v>92149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445498</v>
+        <v>445329</v>
       </c>
       <c r="R7" t="n">
-        <v>7039495</v>
+        <v>7039252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>127843096</v>
       </c>
       <c r="B8" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>127843065</v>
       </c>
       <c r="B9" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127843087</v>
       </c>
       <c r="B10" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -801,53 +801,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843073</v>
+        <v>127843069</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445421</v>
+        <v>445397</v>
       </c>
       <c r="R3" t="n">
-        <v>7039444</v>
+        <v>7039448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,45 +898,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843069</v>
+        <v>127843073</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445397</v>
+        <v>445421</v>
       </c>
       <c r="R4" t="n">
-        <v>7039448</v>
+        <v>7039444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843097</v>
+        <v>127843068</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>92149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445498</v>
+        <v>445329</v>
       </c>
       <c r="R5" t="n">
-        <v>7039495</v>
+        <v>7039252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843068</v>
+        <v>127843097</v>
       </c>
       <c r="B7" t="n">
-        <v>92149</v>
+        <v>100753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445329</v>
+        <v>445498</v>
       </c>
       <c r="R7" t="n">
-        <v>7039252</v>
+        <v>7039495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1100,32 +1100,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843089</v>
+        <v>127843097</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>100753</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445297</v>
+        <v>445498</v>
       </c>
       <c r="R6" t="n">
-        <v>7039205</v>
+        <v>7039495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,32 +1197,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843097</v>
+        <v>127843089</v>
       </c>
       <c r="B7" t="n">
-        <v>100753</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445498</v>
+        <v>445297</v>
       </c>
       <c r="R7" t="n">
-        <v>7039495</v>
+        <v>7039205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,6 +1583,649 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129763762</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92542</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445336</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039420</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129763738</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95994</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445333</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039400</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129763763</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445336</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039418</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129763743</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92542</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>445337</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7039303</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129763761</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>445315</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039364</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129763740</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95994</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>445344</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039393</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
         <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129763763</v>
+        <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>100957</v>
+        <v>92543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445336</v>
+        <v>445337</v>
       </c>
       <c r="R13" t="n">
-        <v>7039418</v>
+        <v>7039303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,6 +1888,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1906,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129763743</v>
+        <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>92542</v>
+        <v>100958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,21 +1918,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1941,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445337</v>
+        <v>445336</v>
       </c>
       <c r="R14" t="n">
-        <v>7039303</v>
+        <v>7039418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1986,7 +1987,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1995,7 +1996,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>92543</v>
+        <v>95995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>95995</v>
+        <v>92543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>95995</v>
+        <v>92548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>92543</v>
+        <v>96000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R12" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>92548</v>
+        <v>96004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>96000</v>
+        <v>92552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92548</v>
+        <v>92552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>96004</v>
+        <v>92554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>92552</v>
+        <v>96006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R12" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92552</v>
+        <v>92554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>92554</v>
+        <v>96006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>96006</v>
+        <v>92554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
         <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>96016</v>
+        <v>92557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>92554</v>
+        <v>96020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R12" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96016</v>
+        <v>96020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>92557</v>
+        <v>96020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>96020</v>
+        <v>92557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>96020</v>
+        <v>92560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>92557</v>
+        <v>96023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R12" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96020</v>
+        <v>96023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B11" t="n">
-        <v>92560</v>
+        <v>96023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B12" t="n">
-        <v>96023</v>
+        <v>92560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1585,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763738</v>
+        <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>96023</v>
+        <v>92561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445333</v>
+        <v>445336</v>
       </c>
       <c r="R11" t="n">
-        <v>7039400</v>
+        <v>7039420</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763762</v>
+        <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>92560</v>
+        <v>96024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445336</v>
+        <v>445333</v>
       </c>
       <c r="R12" t="n">
-        <v>7039420</v>
+        <v>7039400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129763743</v>
+        <v>129763763</v>
       </c>
       <c r="B13" t="n">
-        <v>92560</v>
+        <v>100987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,21 +1810,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445337</v>
+        <v>445336</v>
       </c>
       <c r="R13" t="n">
-        <v>7039303</v>
+        <v>7039418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,7 +1888,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1907,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129763763</v>
+        <v>129763743</v>
       </c>
       <c r="B14" t="n">
-        <v>100986</v>
+        <v>92561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,21 +1917,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445336</v>
+        <v>445337</v>
       </c>
       <c r="R14" t="n">
-        <v>7039418</v>
+        <v>7039303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1977,7 +1976,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1987,7 +1986,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,6 +1995,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96023</v>
+        <v>96024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
         <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>92561</v>
+        <v>92578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>96024</v>
+        <v>96041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>129763763</v>
       </c>
       <c r="B13" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>129763743</v>
       </c>
       <c r="B14" t="n">
-        <v>92561</v>
+        <v>92578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96024</v>
+        <v>96041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
         <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>92594</v>
+        <v>92735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>96057</v>
+        <v>96200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92594</v>
+        <v>92735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>101020</v>
+        <v>101163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96057</v>
+        <v>96200</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
         <v>129763762</v>
       </c>
       <c r="B11" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129763738</v>
       </c>
       <c r="B12" t="n">
-        <v>96234</v>
+        <v>96235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>129763743</v>
       </c>
       <c r="B13" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129763763</v>
       </c>
       <c r="B14" t="n">
-        <v>101216</v>
+        <v>101217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129763761</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129763740</v>
       </c>
       <c r="B16" t="n">
-        <v>96234</v>
+        <v>96235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90848658</v>
+        <v>127843087</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storvallen-Kaxås, Jmt</t>
+          <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445423.8540202606</v>
+        <v>445301</v>
       </c>
       <c r="R2" t="n">
-        <v>7039482.815278382</v>
+        <v>7039216</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,62 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127843069</v>
+        <v>127843065</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445397</v>
+        <v>445361</v>
       </c>
       <c r="R3" t="n">
-        <v>7039448</v>
+        <v>7039366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843073</v>
+        <v>127843066</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445421</v>
+        <v>445516</v>
       </c>
       <c r="R4" t="n">
-        <v>7039444</v>
+        <v>7039494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843068</v>
+        <v>129763738</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>HStorvallen Kaxås, Jmt</t>
+          <t>Storvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445329</v>
+        <v>445333</v>
       </c>
       <c r="R5" t="n">
-        <v>7039252</v>
+        <v>7039400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843097</v>
+        <v>129763740</v>
       </c>
       <c r="B6" t="n">
-        <v>100753</v>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,34 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HStorvallen Kaxås, Jmt</t>
+          <t>Storvallen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445498</v>
+        <v>445344</v>
       </c>
       <c r="R6" t="n">
-        <v>7039495</v>
+        <v>7039393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,44 +1168,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843089</v>
+        <v>127843068</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445297</v>
+        <v>445329</v>
       </c>
       <c r="R7" t="n">
-        <v>7039205</v>
+        <v>7039252</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843096</v>
+        <v>127843069</v>
       </c>
       <c r="B8" t="n">
-        <v>100753</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445438</v>
+        <v>445397</v>
       </c>
       <c r="R8" t="n">
-        <v>7039487</v>
+        <v>7039448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,45 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843065</v>
+        <v>129763743</v>
       </c>
       <c r="B9" t="n">
-        <v>91452</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>HStorvallen Kaxås, Jmt</t>
+          <t>Storvallen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445361</v>
+        <v>445337</v>
       </c>
       <c r="R9" t="n">
-        <v>7039366</v>
+        <v>7039303</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,12 +1439,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,63 +1463,64 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843087</v>
+        <v>129763762</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>HStorvallen Kaxås, Jmt</t>
+          <t>Storvallen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445301</v>
+        <v>445336</v>
       </c>
       <c r="R10" t="n">
-        <v>7039216</v>
+        <v>7039420</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,12 +1547,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,57 +1577,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129763762</v>
+        <v>127843089</v>
       </c>
       <c r="B11" t="n">
-        <v>92769</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storvallen, Jmt</t>
+          <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445336</v>
+        <v>445297</v>
       </c>
       <c r="R11" t="n">
-        <v>7039420</v>
+        <v>7039205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,22 +1654,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,44 +1674,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129763738</v>
+        <v>129763761</v>
       </c>
       <c r="B12" t="n">
-        <v>96235</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1727,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445333</v>
+        <v>445315</v>
       </c>
       <c r="R12" t="n">
-        <v>7039400</v>
+        <v>7039364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1756,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1772,7 +1766,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1799,48 +1793,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129763743</v>
+        <v>90848668</v>
       </c>
       <c r="B13" t="n">
-        <v>92769</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storvallen, Jmt</t>
+          <t>Storvallen-Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445337</v>
+        <v>445452</v>
       </c>
       <c r="R13" t="n">
-        <v>7039303</v>
+        <v>7039329</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1864,22 +1858,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,29 +1872,47 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Klen rönn</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129763763</v>
+        <v>90848667</v>
       </c>
       <c r="B14" t="n">
-        <v>101217</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,37 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storvallen, Jmt</t>
+          <t>Storvallen-Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445336</v>
+        <v>445452</v>
       </c>
       <c r="R14" t="n">
-        <v>7039418</v>
+        <v>7039329</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1972,22 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,26 +1990,45 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Klen rönn</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129763761</v>
+        <v>127843073</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,34 +2036,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storvallen, Jmt</t>
+          <t>HStorvallen Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445315</v>
+        <v>445421</v>
       </c>
       <c r="R15" t="n">
-        <v>7039364</v>
+        <v>7039444</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,22 +2098,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2109,22 +2118,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129763740</v>
+        <v>90848658</v>
       </c>
       <c r="B16" t="n">
-        <v>96235</v>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,37 +2141,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storvallen, Jmt</t>
+          <t>Storvallen-Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445344</v>
+        <v>445424</v>
       </c>
       <c r="R16" t="n">
-        <v>7039393</v>
+        <v>7039483</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2186,22 +2195,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2019-08-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,19 +2211,334 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127843096</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>445438</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039487</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127843097</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>HStorvallen Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>445498</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039495</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129763763</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>445336</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7039418</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35883-2025 artfynd.xlsx
+++ b/artfynd/A 35883-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843087</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843065</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763738</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843069</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763743</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763762</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843089</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1790,6 +1845,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763761</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848668</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848667</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843073</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2238,6 +2313,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848658</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2335,6 +2415,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843096</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2432,6 +2517,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127843097</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2539,8 +2629,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129763763</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>